--- a/ATP_Player_Scouting top150.xlsx
+++ b/ATP_Player_Scouting top150.xlsx
@@ -2990,7 +2990,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Counter-puncher / clean baseliner</t>
+          <t>Serve-first clean baseliner (NOT a counter-puncher: hold 95. pct, return 14. pct — measured 26.09.2026)</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Lefty grinder / retriever</t>
+          <t>Lefty grinder (rally tolerance; return only mid-pack, 45. pct — measured 26.09.2026)</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Counter-puncher / retriever</t>
+          <t>Counter-puncher (movement-based; return pts won only 25. pct — measured 26.09.2026)</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>Serve-led aggressive baseliner</t>
+          <t>Aggressive baseliner, serve-led style (big-ace serve, but serve pts won only 41. pct — measured 26.09.2026)</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>Strong serve plus first-strike power off the ground [hold 79.3%, return 40.2%, aces/match 9.71]</t>
+          <t>Big-ace serve (9.7 aces per 100 serve pts) plus first-strike power off the ground; serve EFFICIENCY below median (62.9% serve pts won = 41. pct, measured 26.09.2026) [hold 79.3%, return 40.2%]</t>
         </is>
       </c>
       <c r="H109" s="3" t="inlineStr">
